--- a/【AI 識詐行動：有聲繪本創作競賽】國中組評分表單-莊宗嚴老師-boyau初審.xlsx
+++ b/【AI 識詐行動：有聲繪本創作競賽】國中組評分表單-莊宗嚴老師-boyau初審.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\_Gm2-共用區\_莊老師區\__AI手冊第二期計畫_20260201-1231\_AI競賽\國中高中組\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GoogDev2T2014_Y530\_Gm2-共用區\筆電共通區\Claude_cowork\AIeval-leave2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1235BF71-72E2-4A57-9232-AFEC4D806AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C93FEF-92B6-41A3-918A-06A13CF55B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="國中組" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="196">
   <si>
     <t>【AI 識詐行動：有聲繪本創作競賽】國中組評分表單</t>
   </si>
@@ -1732,6 +1732,16 @@
     <t>https://youtu.be/CEZyj5Wbk7U</t>
     <phoneticPr fontId="21" type="noConversion"/>
   </si>
+  <si>
+    <t>https://o365kh-my.sharepoint.com/personal/justbeingfun_o365_kh_edu_tw/_layouts/15/stream.aspx?id=%2Fpersonal%2Fjustbeingfun%5Fo365%5Fkh%5Fedu%5Ftw%2FDocuments%2F20%5F%E5%88%86%E4%BA%AB%E5%8D%80%2F114%20AI%20%E7%B9%AA%E6%9C%AC%2F%E7%AC%AC1%E7%B5%84%EF%BC%88%E6%9F%8F%E9%9C%96%E3%80%81%E5%AE%A5%E7%91%8B%E3%80%81%E5%93%81%E5%AE%8F%EF%BC%89%2F4%2E%20%E4%BD%9C%E5%93%81%E7%B9%AA%E6%9C%AC%E5%BD%B1%E7%89%87%EF%BC%88%E7%9B%B4%E6%8E%A5%E4%B8%9F%E9%80%B2%E4%BE%86%EF%BC%89%2F%E5%A4%A7%E6%A9%98%E7%9A%84%E8%99%9B%E5%AF%B6%E4%BF%9D%E8%A1%9B%E6%88%B0%2Emp4&amp;nav=eyJyZWZlcnJhbEluZm8iOnsicmVmZXJyYWxBcHAiOiJPbmVEcml2ZUZvckJ1c2luZXNzIiwicmVmZXJyYWxBcHBQbGF0Zm9ybSI6IldlYiIsInJlZmVycmFsTW9kZSI6InZpZXciLCJyZWZlcnJhbFZpZXciOiJNeUZpbGVzTGlua0NvcHkifX0&amp;ga=1https://o365kh-
+my.sharepoint.com/:v:/g/personal/justbeingfun_o365_kh_edu_t
+w/IQDmNkgn3ynlSqlkz530pUExAbDVSmEWIJ7iL5isdrxEeWI?nav=
+eyJyZWZlcnJhbEluZm8iOnsicmVmZXJyYWxBcHAiOiJPbmVEcml2Z
+UZvckJ1c2luZXNzIiwicmVmZXJyYWxBcHBQbGF0Zm9ybSI6IldlYiIsI
+nJlZmVycmFsTW9kZSI6InZpZXciLCJyZWZlcnJhbFZpZXciOiJNeUZpb
+GVzTGlua0NvcHkifX0&amp;e=HpnHSA</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -2123,7 +2133,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2207,11 +2217,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2221,16 +2226,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -2471,39 +2484,39 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AB1000"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.453125" customWidth="1"/>
-    <col min="2" max="2" width="39.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.26953125" customWidth="1"/>
-    <col min="4" max="4" width="14.453125" customWidth="1"/>
-    <col min="5" max="5" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.453125" customWidth="1"/>
-    <col min="7" max="7" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.81640625" customWidth="1"/>
-    <col min="9" max="9" width="35.1796875" customWidth="1"/>
-    <col min="10" max="10" width="28.54296875" customWidth="1"/>
-    <col min="11" max="11" width="6.81640625" customWidth="1"/>
-    <col min="12" max="12" width="9.26953125" customWidth="1"/>
-    <col min="13" max="13" width="10.1796875" customWidth="1"/>
-    <col min="14" max="14" width="10.453125" customWidth="1"/>
-    <col min="15" max="15" width="30.1796875" customWidth="1"/>
-    <col min="16" max="16" width="10.81640625" customWidth="1"/>
-    <col min="17" max="17" width="74.453125" customWidth="1"/>
-    <col min="18" max="28" width="13.54296875" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="39.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.85546875" customWidth="1"/>
+    <col min="9" max="9" width="35.140625" customWidth="1"/>
+    <col min="10" max="10" width="40.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.85546875" customWidth="1"/>
+    <col min="12" max="12" width="9.28515625" customWidth="1"/>
+    <col min="13" max="13" width="10.140625" customWidth="1"/>
+    <col min="14" max="14" width="10.42578125" customWidth="1"/>
+    <col min="15" max="15" width="30.140625" customWidth="1"/>
+    <col min="16" max="16" width="10.85546875" customWidth="1"/>
+    <col min="17" max="17" width="74.42578125" customWidth="1"/>
+    <col min="18" max="28" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="42.75" customHeight="1">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -2533,10 +2546,10 @@
       <c r="F2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="43" t="s">
+      <c r="G2" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="42"/>
+      <c r="H2" s="39"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -2557,11 +2570,11 @@
       <c r="AA2" s="1"/>
       <c r="AB2" s="1"/>
     </row>
-    <row r="3" spans="1:28" ht="34">
-      <c r="A3" s="44" t="s">
+    <row r="3" spans="1:28" ht="33">
+      <c r="A3" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="40"/>
+      <c r="B3" s="37"/>
       <c r="C3" s="4" t="s">
         <v>190</v>
       </c>
@@ -2602,10 +2615,10 @@
       <c r="AB3" s="1"/>
     </row>
     <row r="4" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="40"/>
+      <c r="B4" s="37"/>
       <c r="C4" s="5">
         <v>0.2</v>
       </c>
@@ -2650,25 +2663,25 @@
       <c r="B5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="37"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="43"/>
       <c r="I5" s="1" t="s">
         <v>167</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="38" t="s">
+      <c r="K5" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="L5" s="39"/>
-      <c r="M5" s="40"/>
+      <c r="L5" s="36"/>
+      <c r="M5" s="37"/>
       <c r="N5" s="7" t="s">
         <v>12</v>
       </c>
@@ -3256,8 +3269,8 @@
       <c r="I14" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>66</v>
+      <c r="J14" s="47" t="s">
+        <v>195</v>
       </c>
       <c r="K14" s="17">
         <v>8</v>
@@ -10940,12 +10953,12 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="19.26953125" customWidth="1"/>
-    <col min="2" max="2" width="5.54296875" customWidth="1"/>
-    <col min="3" max="3" width="62.453125" customWidth="1"/>
-    <col min="4" max="26" width="9.54296875" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" customWidth="1"/>
+    <col min="3" max="3" width="62.42578125" customWidth="1"/>
+    <col min="4" max="26" width="9.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1">
@@ -17938,10 +17951,10 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="52.54296875" customWidth="1"/>
-    <col min="2" max="26" width="9.54296875" customWidth="1"/>
+    <col min="1" max="1" width="52.5703125" customWidth="1"/>
+    <col min="2" max="26" width="9.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1">
@@ -24911,26 +24924,26 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:U1000"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.453125" customWidth="1"/>
-    <col min="2" max="2" width="39.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.54296875" customWidth="1"/>
-    <col min="4" max="4" width="6.81640625" customWidth="1"/>
-    <col min="5" max="5" width="9.26953125" customWidth="1"/>
-    <col min="6" max="6" width="10.1796875" customWidth="1"/>
-    <col min="7" max="7" width="10.453125" customWidth="1"/>
-    <col min="8" max="8" width="30.1796875" customWidth="1"/>
-    <col min="9" max="9" width="10.81640625" customWidth="1"/>
-    <col min="10" max="10" width="74.453125" customWidth="1"/>
-    <col min="11" max="21" width="13.54296875" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="39.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="6.85546875" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" customWidth="1"/>
+    <col min="8" max="8" width="30.140625" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" customWidth="1"/>
+    <col min="10" max="10" width="74.42578125" customWidth="1"/>
+    <col min="11" max="21" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="42.75" customHeight="1">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="42"/>
+      <c r="B1" s="39"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -24974,11 +24987,11 @@
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
     </row>
-    <row r="3" spans="1:21" ht="17">
-      <c r="A3" s="44" t="s">
+    <row r="3" spans="1:21" ht="16.5">
+      <c r="A3" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="40"/>
+      <c r="B3" s="37"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -25000,10 +25013,10 @@
       <c r="U3" s="1"/>
     </row>
     <row r="4" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="40"/>
+      <c r="B4" s="37"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -25034,11 +25047,11 @@
       <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="38" t="s">
+      <c r="D5" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="39"/>
-      <c r="F5" s="40"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="37"/>
       <c r="G5" s="7" t="s">
         <v>12</v>
       </c>

--- a/【AI 識詐行動：有聲繪本創作競賽】國中組評分表單-莊宗嚴老師-boyau初審.xlsx
+++ b/【AI 識詐行動：有聲繪本創作競賽】國中組評分表單-莊宗嚴老師-boyau初審.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GoogDev2T2014_Y530\_Gm2-共用區\筆電共通區\Claude_cowork\AIeval-leave2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C93FEF-92B6-41A3-918A-06A13CF55B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF340C2F-1785-4B1F-B725-785BB0013EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1733,13 +1733,7 @@
     <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
-    <t>https://o365kh-my.sharepoint.com/personal/justbeingfun_o365_kh_edu_tw/_layouts/15/stream.aspx?id=%2Fpersonal%2Fjustbeingfun%5Fo365%5Fkh%5Fedu%5Ftw%2FDocuments%2F20%5F%E5%88%86%E4%BA%AB%E5%8D%80%2F114%20AI%20%E7%B9%AA%E6%9C%AC%2F%E7%AC%AC1%E7%B5%84%EF%BC%88%E6%9F%8F%E9%9C%96%E3%80%81%E5%AE%A5%E7%91%8B%E3%80%81%E5%93%81%E5%AE%8F%EF%BC%89%2F4%2E%20%E4%BD%9C%E5%93%81%E7%B9%AA%E6%9C%AC%E5%BD%B1%E7%89%87%EF%BC%88%E7%9B%B4%E6%8E%A5%E4%B8%9F%E9%80%B2%E4%BE%86%EF%BC%89%2F%E5%A4%A7%E6%A9%98%E7%9A%84%E8%99%9B%E5%AF%B6%E4%BF%9D%E8%A1%9B%E6%88%B0%2Emp4&amp;nav=eyJyZWZlcnJhbEluZm8iOnsicmVmZXJyYWxBcHAiOiJPbmVEcml2ZUZvckJ1c2luZXNzIiwicmVmZXJyYWxBcHBQbGF0Zm9ybSI6IldlYiIsInJlZmVycmFsTW9kZSI6InZpZXciLCJyZWZlcnJhbFZpZXciOiJNeUZpbGVzTGlua0NvcHkifX0&amp;ga=1https://o365kh-
-my.sharepoint.com/:v:/g/personal/justbeingfun_o365_kh_edu_t
-w/IQDmNkgn3ynlSqlkz530pUExAbDVSmEWIJ7iL5isdrxEeWI?nav=
-eyJyZWZlcnJhbEluZm8iOnsicmVmZXJyYWxBcHAiOiJPbmVEcml2Z
-UZvckJ1c2luZXNzIiwicmVmZXJyYWxBcHBQbGF0Zm9ybSI6IldlYiIsI
-nJlZmVycmFsTW9kZSI6InZpZXciLCJyZWZlcnJhbFZpZXciOiJNeUZpb
-GVzTGlua0NvcHkifX0&amp;e=HpnHSA</t>
+    <t>https://youtu.be/TrszNXYubHM</t>
     <phoneticPr fontId="21" type="noConversion"/>
   </si>
 </sst>
@@ -2217,6 +2211,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2226,24 +2228,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -2507,16 +2501,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="42.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -2549,7 +2543,7 @@
       <c r="G2" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="39"/>
+      <c r="H2" s="43"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -2571,10 +2565,10 @@
       <c r="AB2" s="1"/>
     </row>
     <row r="3" spans="1:28" ht="33">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="37"/>
+      <c r="B3" s="41"/>
       <c r="C3" s="4" t="s">
         <v>190</v>
       </c>
@@ -2590,7 +2584,7 @@
       <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="45" t="s">
+      <c r="H3" s="46" t="s">
         <v>5</v>
       </c>
       <c r="I3" s="31"/>
@@ -2615,10 +2609,10 @@
       <c r="AB3" s="1"/>
     </row>
     <row r="4" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="37"/>
+      <c r="B4" s="41"/>
       <c r="C4" s="5">
         <v>0.2</v>
       </c>
@@ -2634,7 +2628,7 @@
       <c r="G4" s="5">
         <v>0.2</v>
       </c>
-      <c r="H4" s="46"/>
+      <c r="H4" s="47"/>
       <c r="I4" s="32"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -2663,25 +2657,25 @@
       <c r="B5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="41" t="s">
+      <c r="C5" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="43"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="38"/>
       <c r="I5" s="1" t="s">
         <v>167</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="35" t="s">
+      <c r="K5" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="L5" s="36"/>
-      <c r="M5" s="37"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="41"/>
       <c r="N5" s="7" t="s">
         <v>12</v>
       </c>
@@ -3269,7 +3263,7 @@
       <c r="I14" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="J14" s="47" t="s">
+      <c r="J14" s="35" t="s">
         <v>195</v>
       </c>
       <c r="K14" s="17">
@@ -10891,7 +10885,7 @@
     <hyperlink ref="B13" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
     <hyperlink ref="J13" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
     <hyperlink ref="B14" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="J14" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="J14" r:id="rId18" display="https://o365kh-my.sharepoint.com/personal/justbeingfun_o365_kh_edu_tw/_layouts/15/stream.aspx?id=%2Fpersonal%2Fjustbeingfun%5Fo365%5Fkh%5Fedu%5Ftw%2FDocuments%2F20%5F%E5%88%86%E4%BA%AB%E5%8D%80%2F114%20AI%20%E7%B9%AA%E6%9C%AC%2F%E7%AC%AC1%E7%B5%84%EF%BC%8" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
     <hyperlink ref="B15" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
     <hyperlink ref="J15" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
     <hyperlink ref="B16" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
@@ -24940,10 +24934,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="42.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -24988,10 +24982,10 @@
       <c r="U2" s="1"/>
     </row>
     <row r="3" spans="1:21" ht="16.5">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="37"/>
+      <c r="B3" s="41"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -25013,10 +25007,10 @@
       <c r="U3" s="1"/>
     </row>
     <row r="4" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="37"/>
+      <c r="B4" s="41"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -25047,11 +25041,11 @@
       <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="36"/>
-      <c r="F5" s="37"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="41"/>
       <c r="G5" s="7" t="s">
         <v>12</v>
       </c>
